--- a/data/trans_dic/P56$privada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$privada-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 73,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,34</t>
+          <t>0,0; 63,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,47</t>
+          <t>0,0; 42,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,42</t>
+          <t>0,0; 73,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,85</t>
+          <t>0,0; 20,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,25</t>
+          <t>0,0; 34,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,61; 74,2</t>
+          <t>19,88; 74,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,82</t>
+          <t>0,0; 60,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,81</t>
+          <t>0,0; 24,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 28,27</t>
+          <t>2,99; 29,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,39; 59,89</t>
+          <t>16,81; 58,89</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,32</t>
+          <t>0,0; 61,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 57,03</t>
+          <t>7,05; 56,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,74</t>
+          <t>0,0; 47,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,26; 38,44</t>
+          <t>8,48; 38,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,63</t>
+          <t>0,0; 38,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 28,5</t>
+          <t>9,69; 27,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,37</t>
+          <t>0,0; 26,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 31,88</t>
+          <t>4,6; 29,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,17</t>
+          <t>0,0; 28,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,38; 29,95</t>
+          <t>12,36; 29,84</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,99</t>
+          <t>0,0; 76,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 26,6</t>
+          <t>2,98; 27,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,65</t>
+          <t>0,0; 51,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,12</t>
+          <t>0,0; 34,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,56; 72,61</t>
+          <t>9,85; 73,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,69; 34,58</t>
+          <t>13,66; 34,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,55</t>
+          <t>0,0; 47,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 27,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,21; 60,64</t>
+          <t>11,07; 62,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 27,77</t>
+          <t>11,57; 26,41</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,87</t>
+          <t>0,0; 64,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,03</t>
+          <t>0,0; 37,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,4</t>
+          <t>0,0; 26,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,2</t>
+          <t>0,0; 40,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,54</t>
+          <t>0,0; 23,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,72</t>
+          <t>0,0; 39,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,32; 41,63</t>
+          <t>15,74; 40,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,47</t>
+          <t>0,0; 38,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 26,14</t>
+          <t>3,3; 26,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 30,88</t>
+          <t>2,43; 32,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,89; 31,75</t>
+          <t>12,11; 30,8</t>
         </is>
       </c>
     </row>
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,87</t>
+          <t>0,0; 38,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,49</t>
+          <t>0,0; 50,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 37,87</t>
+          <t>5,04; 38,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,55</t>
+          <t>0,0; 55,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 30,1</t>
+          <t>6,59; 29,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,49</t>
+          <t>0,0; 44,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 34,1</t>
+          <t>4,18; 36,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,93</t>
+          <t>0,0; 52,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,62; 27,57</t>
+          <t>7,94; 26,82</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,97</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,22</t>
+          <t>0,0; 50,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,89</t>
+          <t>0,0; 31,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,19; 30,82</t>
+          <t>7,19; 31,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,38</t>
+          <t>0,0; 56,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,33; 46,99</t>
+          <t>5,24; 42,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,03</t>
+          <t>0,0; 43,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,99; 22,02</t>
+          <t>7,61; 22,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,53; 52,19</t>
+          <t>6,43; 52,84</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,66; 34,02</t>
+          <t>6,93; 34,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 36,38</t>
+          <t>2,71; 35,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,08; 21,26</t>
+          <t>9,26; 21,38</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,53</t>
+          <t>0,0; 64,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,62</t>
+          <t>0,0; 39,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,6; 39,08</t>
+          <t>4,5; 39,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,0</t>
+          <t>0,0; 29,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,19; 41,24</t>
+          <t>8,55; 40,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 29,17</t>
+          <t>5,86; 29,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 21,07</t>
+          <t>4,19; 20,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,66</t>
+          <t>0,0; 38,74</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,54; 34,14</t>
+          <t>9,67; 34,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 26,83</t>
+          <t>8,3; 27,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 17,9</t>
+          <t>4,31; 17,66</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,26</t>
+          <t>0,0; 43,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,5; 34,71</t>
+          <t>5,96; 34,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,73</t>
+          <t>0,0; 23,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,56; 29,3</t>
+          <t>3,58; 29,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,58; 40,86</t>
+          <t>5,65; 41,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,79; 27,92</t>
+          <t>11,14; 26,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,54</t>
+          <t>0,0; 14,26</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,68; 20,54</t>
+          <t>2,68; 22,01</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,35; 34,0</t>
+          <t>4,1; 35,38</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,27; 25,46</t>
+          <t>12,22; 25,61</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,78; 16,46</t>
+          <t>1,77; 16,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,0; 17,28</t>
+          <t>3,93; 18,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,35; 22,84</t>
+          <t>7,05; 22,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,8; 21,04</t>
+          <t>10,34; 21,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,86; 19,65</t>
+          <t>5,63; 19,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,76; 20,84</t>
+          <t>9,85; 19,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,66; 22,64</t>
+          <t>9,59; 22,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,91; 21,71</t>
+          <t>15,01; 22,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,77; 15,98</t>
+          <t>6,11; 16,57</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,71; 18,01</t>
+          <t>9,01; 17,61</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,24; 20,07</t>
+          <t>10,64; 20,96</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,37; 20,3</t>
+          <t>14,44; 20,36</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 2571</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4043</t>
+          <t>0; 4455</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3722</t>
+          <t>0; 4256</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3441</t>
+          <t>0; 3684</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1366</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5277</t>
+          <t>0; 4384</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6851</t>
+          <t>0; 6430</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1860; 6104</t>
+          <t>1635; 6104</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3423</t>
+          <t>0; 3587</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6170</t>
+          <t>0; 6972</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>816; 8006</t>
+          <t>848; 8276</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2305; 7939</t>
+          <t>2228; 7806</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1599</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2194</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3199</t>
+          <t>0; 3361</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>868; 6958</t>
+          <t>860; 6947</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6139</t>
+          <t>0; 6986</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3048; 14186</t>
+          <t>3129; 14380</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7061</t>
+          <t>0; 6863</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4072; 11948</t>
+          <t>4062; 11696</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 7421</t>
+          <t>0; 5810</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3365; 15500</t>
+          <t>2238; 14376</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6565</t>
+          <t>0; 6685</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6697; 16207</t>
+          <t>6687; 16152</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1303</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4568</t>
+          <t>0; 4593</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535; 4871</t>
+          <t>546; 4952</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6452</t>
+          <t>0; 6345</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6571</t>
+          <t>0; 6582</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1030; 7823</t>
+          <t>1062; 7957</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4586; 11587</t>
+          <t>4576; 11661</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6765</t>
+          <t>0; 7153</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 6796</t>
+          <t>0; 7733</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2050; 10178</t>
+          <t>1858; 10413</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6075; 14393</t>
+          <t>5996; 13685</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1146</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5460</t>
+          <t>0; 5571</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3605</t>
+          <t>0; 3712</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3470</t>
+          <t>0; 2489</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5429</t>
+          <t>0; 4355</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5286</t>
+          <t>0; 5200</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 10148</t>
+          <t>0; 9723</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3227; 8231</t>
+          <t>3112; 8042</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4483</t>
+          <t>0; 5133</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1032; 8139</t>
+          <t>1027; 8336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>870; 10785</t>
+          <t>849; 11514</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3455; 9221</t>
+          <t>3517; 8946</t>
         </is>
       </c>
     </row>
@@ -3051,52 +3051,52 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 616</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3290</t>
+          <t>0; 2888</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5495</t>
+          <t>0; 4555</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>992; 7460</t>
+          <t>993; 7504</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5761</t>
+          <t>0; 6719</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1202; 4992</t>
+          <t>1093; 4908</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6145</t>
+          <t>0; 5935</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1102; 9003</t>
+          <t>1104; 9730</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 6318</t>
+          <t>0; 6714</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1835; 6641</t>
+          <t>1912; 6460</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2838</t>
+          <t>0; 3687</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5348</t>
+          <t>0; 5341</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3448</t>
+          <t>0; 3368</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1189; 5093</t>
+          <t>1189; 5199</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6790</t>
+          <t>0; 6006</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1075; 9490</t>
+          <t>1058; 8538</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 8849</t>
+          <t>0; 9541</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2220; 6993</t>
+          <t>2416; 7028</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>929; 7429</t>
+          <t>916; 7521</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2055; 10493</t>
+          <t>2137; 10584</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>907; 11977</t>
+          <t>892; 11588</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4386; 10264</t>
+          <t>4471; 10323</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3399</t>
+          <t>0; 3327</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 7249</t>
+          <t>0; 6118</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>917; 7796</t>
+          <t>898; 7868</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3846</t>
+          <t>0; 3608</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1433</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3256; 14610</t>
+          <t>3028; 14311</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2526; 12515</t>
+          <t>2514; 12820</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1904; 8834</t>
+          <t>1759; 8610</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3442</t>
+          <t>0; 3541</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4355; 17403</t>
+          <t>4931; 17343</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4793; 16862</t>
+          <t>5214; 17508</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2376; 9726</t>
+          <t>2343; 9598</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 1660</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2066</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4029</t>
+          <t>0; 3944</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1768; 7220</t>
+          <t>1240; 7108</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 7403</t>
+          <t>0; 6973</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1069; 8807</t>
+          <t>1076; 8910</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1269; 9300</t>
+          <t>1286; 9397</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6762; 16006</t>
+          <t>6384; 15270</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 7146</t>
+          <t>0; 7007</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1043; 8000</t>
+          <t>1044; 8571</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1386; 10833</t>
+          <t>1307; 11275</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>9585; 19896</t>
+          <t>9546; 20008</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>858; 7949</t>
+          <t>854; 7968</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3142; 13566</t>
+          <t>3089; 14249</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5299; 16468</t>
+          <t>5085; 16395</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10000; 21474</t>
+          <t>10552; 22156</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5480; 18381</t>
+          <t>5267; 18327</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20026; 42779</t>
+          <t>20218; 40510</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16591; 38885</t>
+          <t>16480; 39014</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>37439; 54507</t>
+          <t>37689; 56308</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8182; 22663</t>
+          <t>8667; 23499</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27548; 51117</t>
+          <t>25556; 49965</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24973; 48944</t>
+          <t>25946; 51109</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>50756; 71672</t>
+          <t>50999; 71897</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$privada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$privada-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,72%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,03</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,18</t>
+          <t>0,0; 56,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,85</t>
+          <t>0,0; 41,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,24</t>
+          <t>0,0; 56,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,65</t>
+          <t>0,0; 26,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,97</t>
+          <t>0,0; 33,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,88; 74,21</t>
+          <t>20,88; 73,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,59</t>
+          <t>0,0; 60,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,65</t>
+          <t>0,0; 25,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 29,22</t>
+          <t>2,92; 28,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,81; 58,89</t>
+          <t>18,46; 58,28</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -867,52 +867,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,28</t>
+          <t>0,0; 69,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 56,94</t>
+          <t>7,55; 57,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,5</t>
+          <t>0,0; 40,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,48; 38,96</t>
+          <t>8,7; 37,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,52</t>
+          <t>0,0; 31,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 27,9</t>
+          <t>9,8; 27,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,91</t>
+          <t>0,0; 28,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 29,57</t>
+          <t>6,68; 30,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,69</t>
+          <t>0,0; 28,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,36; 29,84</t>
+          <t>12,17; 29,88</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,4</t>
+          <t>0,0; 75,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 27,04</t>
+          <t>3,09; 26,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,78</t>
+          <t>0,0; 55,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,18</t>
+          <t>0,0; 37,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,85; 73,85</t>
+          <t>9,21; 72,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,66; 34,8</t>
+          <t>13,95; 35,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,1</t>
+          <t>0,0; 43,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,11</t>
+          <t>0,0; 22,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,07; 62,04</t>
+          <t>11,98; 59,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,57; 26,41</t>
+          <t>11,74; 27,23</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -1142,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,15</t>
+          <t>0,0; 63,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,1</t>
+          <t>0,0; 35,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,83</t>
+          <t>0,0; 25,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,27</t>
+          <t>0,0; 49,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,16</t>
+          <t>0,0; 27,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,01</t>
+          <t>0,0; 38,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,74; 40,67</t>
+          <t>15,97; 40,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,32</t>
+          <t>0,0; 39,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 26,77</t>
+          <t>3,32; 24,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 32,96</t>
+          <t>2,56; 31,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,11; 30,8</t>
+          <t>11,21; 30,3</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,76</t>
+          <t>0,0; 66,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,51</t>
+          <t>0,0; 37,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,97</t>
+          <t>0,0; 62,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 38,09</t>
+          <t>5,01; 38,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,46</t>
+          <t>0,0; 48,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 29,6</t>
+          <t>7,09; 29,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,91</t>
+          <t>0,0; 44,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 36,85</t>
+          <t>4,18; 33,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,0</t>
+          <t>0,0; 50,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,94; 26,82</t>
+          <t>7,85; 27,6</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 76,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,15</t>
+          <t>0,0; 45,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,15</t>
+          <t>0,0; 38,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,19; 31,46</t>
+          <t>7,14; 30,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,94</t>
+          <t>0,0; 61,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,24; 42,28</t>
+          <t>5,38; 47,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,16</t>
+          <t>0,0; 44,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,61; 22,13</t>
+          <t>7,49; 22,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,43; 52,84</t>
+          <t>6,36; 53,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 34,31</t>
+          <t>6,71; 33,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 35,2</t>
+          <t>2,73; 35,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,26; 21,38</t>
+          <t>9,43; 22,11</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,15</t>
+          <t>0,0; 67,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,34</t>
+          <t>0,0; 39,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 39,44</t>
+          <t>4,46; 39,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,08</t>
+          <t>0,0; 27,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,55; 40,39</t>
+          <t>9,19; 39,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,86; 29,88</t>
+          <t>5,89; 30,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,19; 20,53</t>
+          <t>4,48; 19,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,74</t>
+          <t>0,0; 39,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,67; 34,02</t>
+          <t>8,45; 33,49</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,3; 27,86</t>
+          <t>7,67; 27,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,31; 17,66</t>
+          <t>4,67; 18,05</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -1707,52 +1707,52 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,32</t>
+          <t>0,0; 44,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,96; 34,17</t>
+          <t>5,77; 31,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,3</t>
+          <t>0,0; 22,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 29,64</t>
+          <t>3,54; 29,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,65; 41,29</t>
+          <t>5,69; 40,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,14; 26,63</t>
+          <t>11,79; 28,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,26</t>
+          <t>0,0; 14,14</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,68; 22,01</t>
+          <t>2,67; 22,15</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,1; 35,38</t>
+          <t>4,15; 32,08</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,22; 25,61</t>
+          <t>12,06; 26,06</t>
         </is>
       </c>
     </row>
@@ -1784,47 +1784,47 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>13,13%</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
           <t>14,89%</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>14,89%</t>
-        </is>
-      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,77; 16,5</t>
+          <t>1,84; 16,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,93; 18,15</t>
+          <t>4,05; 18,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,05; 22,74</t>
+          <t>7,12; 22,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,34; 21,71</t>
+          <t>10,05; 21,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,63; 19,59</t>
+          <t>5,61; 20,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,85; 19,74</t>
+          <t>9,59; 20,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,59; 22,71</t>
+          <t>9,47; 23,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,01; 22,43</t>
+          <t>14,93; 21,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,11; 16,57</t>
+          <t>5,55; 16,22</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,01; 17,61</t>
+          <t>9,24; 17,41</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,64; 20,96</t>
+          <t>10,5; 20,87</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,44; 20,36</t>
+          <t>14,4; 20,51</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4763</t>
         </is>
       </c>
     </row>
@@ -2209,22 +2209,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2571</t>
+          <t>0; 3520</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4455</t>
+          <t>0; 4017</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4256</t>
+          <t>0; 4126</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3684</t>
+          <t>0; 2992</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4384</t>
+          <t>0; 5683</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6430</t>
+          <t>0; 6119</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1635; 6104</t>
+          <t>1766; 6248</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3587</t>
+          <t>0; 3578</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6972</t>
+          <t>0; 7187</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>848; 8276</t>
+          <t>826; 8045</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2228; 7806</t>
+          <t>2533; 7997</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10574</t>
+          <t>11416</t>
         </is>
       </c>
     </row>
@@ -2427,52 +2427,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3361</t>
+          <t>0; 3814</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>860; 6947</t>
+          <t>987; 7522</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6986</t>
+          <t>0; 5989</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3129; 14380</t>
+          <t>3211; 13978</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6863</t>
+          <t>0; 5674</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4062; 11696</t>
+          <t>4383; 12498</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5810</t>
+          <t>0; 6099</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2238; 14376</t>
+          <t>3246; 14975</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6685</t>
+          <t>0; 6751</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6687; 16152</t>
+          <t>7034; 17271</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7493</t>
+          <t>7670</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>9811</t>
         </is>
       </c>
     </row>
@@ -2635,52 +2635,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4593</t>
+          <t>0; 4548</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>546; 4952</t>
+          <t>553; 4824</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6345</t>
+          <t>0; 6795</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6582</t>
+          <t>0; 7178</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1062; 7957</t>
+          <t>992; 7772</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4576; 11661</t>
+          <t>4679; 11917</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 7153</t>
+          <t>0; 6635</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 7733</t>
+          <t>0; 6506</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1858; 10413</t>
+          <t>2010; 10038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5996; 13685</t>
+          <t>6036; 14002</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>6037</t>
         </is>
       </c>
     </row>
@@ -2838,57 +2838,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5571</t>
+          <t>0; 5552</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3712</t>
+          <t>0; 3574</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2489</t>
+          <t>0; 2465</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4355</t>
+          <t>0; 5402</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5200</t>
+          <t>0; 6272</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 9723</t>
+          <t>0; 9562</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3112; 8042</t>
+          <t>3325; 8469</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5133</t>
+          <t>0; 5340</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1027; 8336</t>
+          <t>1033; 7669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>849; 11514</t>
+          <t>893; 11147</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3517; 8946</t>
+          <t>3401; 9192</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3970</t>
         </is>
       </c>
     </row>
@@ -3056,47 +3056,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2888</t>
+          <t>0; 2869</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4555</t>
+          <t>0; 5577</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>993; 7504</t>
+          <t>986; 7520</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6719</t>
+          <t>0; 5894</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1093; 4908</t>
+          <t>1221; 5110</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5935</t>
+          <t>0; 5851</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1104; 9730</t>
+          <t>1104; 8868</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 6714</t>
+          <t>0; 6564</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1912; 6460</t>
+          <t>1953; 6871</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>7179</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3687</t>
+          <t>0; 2838</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5341</t>
+          <t>0; 4872</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3368</t>
+          <t>0; 4183</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1189; 5199</t>
+          <t>1182; 5109</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6006</t>
+          <t>0; 6434</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1058; 8538</t>
+          <t>1086; 9596</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 9541</t>
+          <t>0; 9871</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2416; 7028</t>
+          <t>2436; 7381</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>916; 7521</t>
+          <t>906; 7610</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2137; 10584</t>
+          <t>2071; 10453</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>892; 11588</t>
+          <t>900; 11582</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4471; 10323</t>
+          <t>4630; 10859</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>6266</t>
         </is>
       </c>
     </row>
@@ -3457,22 +3457,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3327</t>
+          <t>0; 3523</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6118</t>
+          <t>0; 6123</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>898; 7868</t>
+          <t>889; 7843</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3608</t>
+          <t>0; 4144</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3028; 14311</t>
+          <t>3256; 14010</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2514; 12820</t>
+          <t>2526; 13151</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1759; 8610</t>
+          <t>2314; 9813</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3541</t>
+          <t>0; 3591</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4931; 17343</t>
+          <t>4308; 17072</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5214; 17508</t>
+          <t>4820; 17456</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2343; 9598</t>
+          <t>3110; 12011</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>14252</t>
+          <t>16562</t>
         </is>
       </c>
     </row>
@@ -3675,52 +3675,52 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3944</t>
+          <t>0; 4043</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1240; 7108</t>
+          <t>1368; 7465</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 6973</t>
+          <t>0; 6754</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1076; 8910</t>
+          <t>1065; 8767</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1286; 9397</t>
+          <t>1294; 9208</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6384; 15270</t>
+          <t>7842; 18937</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 7007</t>
+          <t>0; 6951</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1044; 8571</t>
+          <t>1040; 8625</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1307; 11275</t>
+          <t>1321; 10222</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>9546; 20008</t>
+          <t>10873; 23504</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>45911</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>61110</t>
+          <t>66003</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>854; 7968</t>
+          <t>887; 7995</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3089; 14249</t>
+          <t>3182; 14551</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5085; 16395</t>
+          <t>5130; 16313</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10552; 22156</t>
+          <t>10915; 22962</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5267; 18327</t>
+          <t>5244; 19030</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20218; 40510</t>
+          <t>19684; 41665</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16480; 39014</t>
+          <t>16272; 40246</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>37689; 56308</t>
+          <t>41110; 59639</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8667; 23499</t>
+          <t>7866; 23003</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>25556; 49965</t>
+          <t>26208; 49401</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25946; 51109</t>
+          <t>25617; 50892</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>50999; 71897</t>
+          <t>55311; 78774</t>
         </is>
       </c>
     </row>
